--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121108666</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121108677</v>
       </c>
       <c r="B3" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121108563</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121108647</v>
       </c>
       <c r="B5" t="n">
-        <v>94737</v>
+        <v>94747</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108666</v>
+        <v>121108647</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>94747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108677</v>
+        <v>121108563</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573411</v>
+        <v>573418</v>
       </c>
       <c r="R3" t="n">
-        <v>6511990</v>
+        <v>6512015</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108563</v>
+        <v>121108677</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>78246</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573418</v>
+        <v>573411</v>
       </c>
       <c r="R4" t="n">
-        <v>6512015</v>
+        <v>6511990</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121108647</v>
+        <v>121108666</v>
       </c>
       <c r="B5" t="n">
-        <v>94747</v>
+        <v>79219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108647</v>
+        <v>121108677</v>
       </c>
       <c r="B2" t="n">
-        <v>94747</v>
+        <v>78249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108563</v>
+        <v>121108647</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>94759</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573418</v>
+        <v>573411</v>
       </c>
       <c r="R3" t="n">
-        <v>6512015</v>
+        <v>6511990</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108677</v>
+        <v>121108666</v>
       </c>
       <c r="B4" t="n">
-        <v>78246</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121108666</v>
+        <v>121108563</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573411</v>
+        <v>573418</v>
       </c>
       <c r="R5" t="n">
-        <v>6511990</v>
+        <v>6512015</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108677</v>
+        <v>121108666</v>
       </c>
       <c r="B2" t="n">
-        <v>78249</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>121108647</v>
       </c>
       <c r="B3" t="n">
-        <v>94759</v>
+        <v>94760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108666</v>
+        <v>121108677</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>78249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,7 +984,7 @@
         <v>121108563</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108666</v>
+        <v>121108677</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>78252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108647</v>
+        <v>121108666</v>
       </c>
       <c r="B3" t="n">
-        <v>94760</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108677</v>
+        <v>121108647</v>
       </c>
       <c r="B4" t="n">
-        <v>78249</v>
+        <v>94763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,7 +984,7 @@
         <v>121108563</v>
       </c>
       <c r="B5" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108677</v>
+        <v>121108647</v>
       </c>
       <c r="B2" t="n">
-        <v>78252</v>
+        <v>94763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108666</v>
+        <v>121108563</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573411</v>
+        <v>573418</v>
       </c>
       <c r="R3" t="n">
-        <v>6511990</v>
+        <v>6512015</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108647</v>
+        <v>121108677</v>
       </c>
       <c r="B4" t="n">
-        <v>94763</v>
+        <v>78252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121108563</v>
+        <v>121108666</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573418</v>
+        <v>573411</v>
       </c>
       <c r="R5" t="n">
-        <v>6512015</v>
+        <v>6511990</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 43283-2024 artfynd.xlsx
+++ b/artfynd/A 43283-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121108647</v>
+        <v>121108677</v>
       </c>
       <c r="B2" t="n">
-        <v>94763</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121108563</v>
+        <v>121108647</v>
       </c>
       <c r="B3" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573418</v>
+        <v>573411</v>
       </c>
       <c r="R3" t="n">
-        <v>6512015</v>
+        <v>6511990</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121108677</v>
+        <v>121108563</v>
       </c>
       <c r="B4" t="n">
-        <v>78252</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573411</v>
+        <v>573418</v>
       </c>
       <c r="R4" t="n">
-        <v>6511990</v>
+        <v>6512015</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,12 +969,7 @@
         <v>121108666</v>
       </c>
       <c r="B5" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
